--- a/03_BOM/DuAn_HighVoltage_V3.2.xlsx
+++ b/03_BOM/DuAn_HighVoltage_V3.2.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="390">
   <si>
     <t>Line #</t>
   </si>
@@ -122,9 +122,6 @@
     <t>1000uF/400V</t>
   </si>
   <si>
-    <t>NO PN</t>
-  </si>
-  <si>
     <t>C13, C14, C15, C16, C17, C18, C19, C20, C21, C22</t>
   </si>
   <si>
@@ -1182,6 +1179,24 @@
   </si>
   <si>
     <t>Không có stock digi</t>
+  </si>
+  <si>
+    <t>B43305A9108M000</t>
+  </si>
+  <si>
+    <t>CAP ALUM 1000UF 20% 400V SNAP TH</t>
+  </si>
+  <si>
+    <t>CAP ALUM 15000UF 20% 63V SNAP TH</t>
+  </si>
+  <si>
+    <t>159LBB063M2EH</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>Cornell Dubilier Knowles</t>
   </si>
 </sst>
 </file>
@@ -1211,7 +1226,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1221,12 +1236,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1306,31 +1315,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1340,6 +1346,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1635,17 +1644,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A1" s="26" t="s">
-        <v>347</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
+      <c r="A1" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.45">
@@ -1668,19 +1677,19 @@
         <v>5</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="I2" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>351</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
@@ -1700,7 +1709,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>12</v>
@@ -1726,7 +1735,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>16</v>
@@ -1752,7 +1761,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1775,7 +1784,9 @@
       <c r="E6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>353</v>
+      </c>
       <c r="G6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1797,7 +1808,9 @@
       <c r="E7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>353</v>
+      </c>
       <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
@@ -1805,54 +1818,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8" t="s">
+    <row r="8" spans="1:11" s="27" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="D8" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="26" t="s">
+        <v>388</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>384</v>
+      </c>
+      <c r="H8" s="26">
+        <v>10</v>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="27" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9">
-        <v>10</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="D9" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9">
+      <c r="E9" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="26" t="s">
+        <v>389</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>387</v>
+      </c>
+      <c r="H9" s="26">
         <v>2</v>
       </c>
-      <c r="K9" s="10" t="s">
-        <v>382</v>
+      <c r="K9" s="27" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
@@ -1860,22 +1881,22 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H10" s="1">
         <v>3</v>
@@ -1886,22 +1907,22 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="H11" s="1">
         <v>15</v>
@@ -1912,22 +1933,22 @@
         <v>7</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="H12" s="1">
         <v>2</v>
@@ -1938,22 +1959,22 @@
         <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H13" s="1">
         <v>2</v>
@@ -1964,22 +1985,22 @@
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
@@ -1990,22 +2011,22 @@
         <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="H15" s="1">
         <v>4</v>
@@ -2016,22 +2037,22 @@
         <v>7</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="F16" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H16" s="1">
         <v>4</v>
@@ -2042,22 +2063,22 @@
         <v>7</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="F17" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H17" s="1">
         <v>2</v>
@@ -2068,22 +2089,22 @@
         <v>7</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="H18" s="1">
         <v>3</v>
@@ -2094,22 +2115,22 @@
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
@@ -2120,22 +2141,22 @@
         <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
@@ -2146,16 +2167,16 @@
         <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="1"/>
@@ -2168,16 +2189,16 @@
         <v>7</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="1"/>
@@ -2185,155 +2206,155 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="14" t="s">
+    <row r="23" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="D23" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="E23" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="F23" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="G23" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="H23" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="15"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="F27" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="G23" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="H23" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F24" s="18"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="F25" s="15" t="s">
+      <c r="G27" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F28" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="G25" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H25" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>360</v>
-      </c>
-      <c r="G26" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H26" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H27" s="16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E28" s="14" t="s">
+      <c r="G28" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="F28" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="H28" s="16">
+      <c r="H28" s="13">
         <v>1</v>
       </c>
     </row>
@@ -2342,22 +2363,22 @@
         <v>7</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>362</v>
+      <c r="F29" s="16" t="s">
+        <v>361</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H29" s="1">
         <v>2</v>
@@ -2368,22 +2389,22 @@
         <v>7</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="H30" s="1">
         <v>1</v>
@@ -2394,22 +2415,22 @@
         <v>7</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="H31" s="1">
         <v>3</v>
@@ -2420,22 +2441,22 @@
         <v>7</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="H32" s="1">
         <v>4</v>
@@ -2446,22 +2467,22 @@
         <v>7</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="E33" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H33" s="1">
         <v>2</v>
@@ -2472,22 +2493,22 @@
         <v>7</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="F34" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H34" s="1">
         <v>3</v>
@@ -2498,22 +2519,22 @@
         <v>7</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="F35" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="H35" s="1">
         <v>2</v>
@@ -2524,22 +2545,22 @@
         <v>7</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="F36" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H36" s="1">
         <v>2</v>
@@ -2550,22 +2571,22 @@
         <v>7</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="F37" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H37" s="1">
         <v>2</v>
@@ -2576,22 +2597,22 @@
         <v>7</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="E38" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H38" s="1">
         <v>1</v>
@@ -2602,22 +2623,22 @@
         <v>7</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="F39" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="H39" s="1">
         <v>8</v>
@@ -2626,22 +2647,22 @@
     <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" s="1"/>
       <c r="B40" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="F40" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="H40" s="1">
         <v>1</v>
@@ -2650,22 +2671,22 @@
     <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" s="1"/>
       <c r="B41" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="E41" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="H41" s="1">
         <v>1</v>
@@ -2676,22 +2697,22 @@
         <v>7</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="E42" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="H42" s="1">
         <v>4</v>
@@ -2702,22 +2723,22 @@
         <v>7</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="E43" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="H43" s="1">
         <v>4</v>
@@ -2728,22 +2749,22 @@
         <v>7</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="H44" s="1">
         <v>13</v>
@@ -2754,22 +2775,22 @@
         <v>7</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="E45" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>369</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="H45" s="1">
         <v>10</v>
@@ -2780,22 +2801,22 @@
         <v>7</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="F46" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="H46" s="1">
         <v>6</v>
@@ -2806,22 +2827,22 @@
         <v>7</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="H47" s="1">
         <v>42</v>
@@ -2832,22 +2853,22 @@
         <v>7</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="E48" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>201</v>
       </c>
       <c r="H48" s="1">
         <v>2</v>
@@ -2858,22 +2879,22 @@
         <v>7</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="E49" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="H49" s="1">
         <v>2</v>
@@ -2884,22 +2905,22 @@
         <v>7</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="H50" s="1">
         <v>34</v>
@@ -2910,22 +2931,22 @@
         <v>7</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="E51" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="G51" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="H51" s="1">
         <v>3</v>
@@ -2936,22 +2957,22 @@
         <v>7</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F52" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="H52" s="1">
         <v>2</v>
@@ -2962,22 +2983,22 @@
         <v>7</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="E53" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="H53" s="1">
         <v>1</v>
@@ -2986,22 +3007,22 @@
     <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" s="1"/>
       <c r="B54" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="E54" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F54" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="G54" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>369</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="H54" s="1">
         <v>1</v>
@@ -3010,22 +3031,22 @@
     <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" s="1"/>
       <c r="B55" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="E55" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G55" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="H55" s="1">
         <v>1</v>
@@ -3036,22 +3057,22 @@
         <v>7</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="E56" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F56" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G56" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F56" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="H56" s="1">
         <v>2</v>
@@ -3062,48 +3083,48 @@
         <v>7</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="E57" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F57" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="H57" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B58" s="11" t="s">
+    <row r="58" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="D58" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="E58" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="E58" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="H58" s="12">
+      <c r="F58" s="8"/>
+      <c r="G58" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="H58" s="9">
         <v>8</v>
       </c>
     </row>
@@ -3112,22 +3133,22 @@
         <v>7</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="E59" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F59" s="19" t="s">
-        <v>368</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="H59" s="1">
         <v>3</v>
@@ -3138,22 +3159,22 @@
         <v>7</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F60" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="G60" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F60" s="19" t="s">
-        <v>369</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="H60" s="1">
         <v>3</v>
@@ -3164,22 +3185,22 @@
         <v>7</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="D61" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="E61" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F61" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F61" s="19" t="s">
-        <v>369</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="H61" s="1">
         <v>1</v>
@@ -3190,48 +3211,48 @@
         <v>7</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="D62" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="E62" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F62" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F62" s="19" t="s">
-        <v>370</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="H62" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B63" s="11" t="s">
+    <row r="63" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="D63" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="E63" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="F63" s="9"/>
+      <c r="G63" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="E63" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="F63" s="12"/>
-      <c r="G63" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="H63" s="12">
+      <c r="H63" s="9">
         <v>2</v>
       </c>
     </row>
@@ -3240,22 +3261,22 @@
         <v>7</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="D64" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="E64" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F64" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F64" s="19" t="s">
-        <v>265</v>
-      </c>
       <c r="G64" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H64" s="1">
         <v>2</v>
@@ -3266,22 +3287,22 @@
         <v>7</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="D65" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="E65" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="F65" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="H65" s="1">
         <v>1</v>
@@ -3292,22 +3313,22 @@
         <v>7</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="D66" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="E66" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>274</v>
-      </c>
       <c r="F66" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H66" s="1">
         <v>2</v>
@@ -3316,22 +3337,22 @@
     <row r="67" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A67" s="1"/>
       <c r="B67" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="D67" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="E67" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="F67" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H67" s="1">
         <v>1</v>
@@ -3342,22 +3363,22 @@
         <v>7</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="D68" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="E68" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="F68" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H68" s="1">
         <v>1</v>
@@ -3368,22 +3389,22 @@
         <v>7</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="D69" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="E69" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="F69" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="G69" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="H69" s="1">
         <v>1</v>
@@ -3394,22 +3415,22 @@
         <v>7</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="D70" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="F70" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="G70" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="H70" s="1">
         <v>2</v>
@@ -3420,22 +3441,22 @@
         <v>7</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="D71" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="E71" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="E71" s="2" t="s">
+      <c r="F71" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="G71" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="H71" s="1">
         <v>2</v>
@@ -3446,22 +3467,22 @@
         <v>7</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="D72" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="E72" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>301</v>
-      </c>
       <c r="F72" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H72" s="1">
         <v>1</v>
@@ -3472,22 +3493,22 @@
         <v>7</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="E73" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H73" s="1">
         <v>2</v>
@@ -3498,22 +3519,22 @@
         <v>7</v>
       </c>
       <c r="B74" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="E74" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="F74" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="H74" s="1">
         <v>1</v>
@@ -3522,22 +3543,22 @@
     <row r="75" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A75" s="1"/>
       <c r="B75" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="E75" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F75" s="21" t="s">
-        <v>375</v>
+      <c r="F75" s="18" t="s">
+        <v>374</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H75" s="1">
         <v>1</v>
@@ -3548,22 +3569,22 @@
         <v>7</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="D76" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="E76" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>317</v>
-      </c>
       <c r="F76" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H76" s="1">
         <v>2</v>
@@ -3574,46 +3595,46 @@
         <v>7</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="D77" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="E77" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>321</v>
-      </c>
       <c r="F77" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H77" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:8" s="24" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A78" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B78" s="22" t="s">
+    <row r="78" spans="1:8" s="21" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" s="19" t="s">
         <v>322</v>
       </c>
-      <c r="C78" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D78" s="22" t="s">
+      <c r="E78" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="E78" s="22" t="s">
-        <v>324</v>
-      </c>
-      <c r="F78" s="23"/>
-      <c r="G78" s="23"/>
-      <c r="H78" s="23">
+      <c r="F78" s="20"/>
+      <c r="G78" s="20"/>
+      <c r="H78" s="20">
         <v>1</v>
       </c>
     </row>
@@ -3622,22 +3643,22 @@
         <v>7</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D79" s="2" t="s">
+      <c r="E79" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>328</v>
       </c>
       <c r="H79" s="1">
         <v>1</v>
@@ -3648,22 +3669,22 @@
         <v>7</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="D80" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="E80" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>332</v>
-      </c>
       <c r="F80" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H80" s="1">
         <v>1</v>
@@ -3674,22 +3695,22 @@
         <v>7</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="D81" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="E81" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="F81" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="G81" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="H81" s="1">
         <v>1</v>
@@ -3700,22 +3721,22 @@
         <v>7</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="D82" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="D82" s="2" t="s">
+      <c r="E82" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="G82" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="H82" s="1">
         <v>1</v>
@@ -3726,37 +3747,37 @@
         <v>7</v>
       </c>
       <c r="B83" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="D83" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="E83" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="F83" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="G83" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="H83" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B85" s="24"/>
-      <c r="C85" s="25" t="s">
+      <c r="B85" s="21"/>
+      <c r="C85" s="22" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B86" s="10"/>
+      <c r="C86" t="s">
         <v>383</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="B86" s="13"/>
-      <c r="C86" t="s">
-        <v>384</v>
       </c>
     </row>
   </sheetData>
